--- a/Checklist de suivi d'audit SMETA.xlsx
+++ b/Checklist de suivi d'audit SMETA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\0-MYC-TN-2026\11- Audit et préparation\2026\SMETA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED6C4D6-FFD6-4E0B-9BBD-890C01ADF8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9CAB4A-1E5F-44C2-B310-B67F86E62A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="115">
   <si>
     <t>Num</t>
   </si>
@@ -76,9 +76,6 @@
 </t>
   </si>
   <si>
-    <t>SL</t>
-  </si>
-  <si>
     <t xml:space="preserve">Organization chart </t>
   </si>
   <si>
@@ -98,9 +95,6 @@
   </si>
   <si>
     <t xml:space="preserve">Copie </t>
-  </si>
-  <si>
-    <t>Chaima</t>
   </si>
   <si>
     <t xml:space="preserve">Employee manual/handbook, Factory rules &amp; regulations/ Disciplinary practices policy and Records </t>
@@ -323,17 +317,6 @@
     <t xml:space="preserve">Certificate of Inspection for Completed Building Construction/ Registration Records </t>
   </si>
   <si>
-    <t>Certificat / document d'enregistrement du bâtiment
-Certificat d'achèvement de construction — si applicable
-Certificat / rapport d'inspection du bâtiment
-Autorisation d'exploitation — si applicable
-Plans architecturaux approuvés
-Documents relatifs aux modifications/extensions
-Documents de sécurité incendie
-Contrat de location — si MYC est locataire
-Documents fournis par le propriétaire</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fire-Fighting Acceptance Inspection Certificate/ Report </t>
   </si>
   <si>
@@ -345,9 +328,6 @@
 Rapports de contrôle du système de détection — si présent
 Rapports de contrôle du réseau incendie — si présent
 Rapports de contrôle de la pompe incendie — si présente</t>
-  </si>
-  <si>
-    <t>Hammadi</t>
   </si>
   <si>
     <t xml:space="preserve">Safety officer Certificate </t>
@@ -436,9 +416,6 @@
 </t>
   </si>
   <si>
-    <t>SP</t>
-  </si>
-  <si>
     <t xml:space="preserve">List of chemical / Approval certificate of chemical warehouse/register &amp; storage record </t>
   </si>
   <si>
@@ -489,9 +466,6 @@
   </si>
   <si>
     <t xml:space="preserve">Politique responsabilité social/procédure d'analyse de risque HSE(RSE)/plan d'audit </t>
-  </si>
-  <si>
-    <t>QMS</t>
   </si>
   <si>
     <t xml:space="preserve">Subcontractors list/ monitoring records on sub-contractors' social responsibilities performance </t>
@@ -575,12 +549,6 @@
   </si>
   <si>
     <t>In progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaima </t>
-  </si>
-  <si>
-    <t>Naoures *2</t>
   </si>
   <si>
     <t>Mettre dans le planning de formation (26/27)</t>
@@ -621,28 +589,33 @@
     <t xml:space="preserve">FDS de tous les produit chimique </t>
   </si>
   <si>
-    <t>HSE/SP</t>
-  </si>
-  <si>
-    <t>RH/G</t>
-  </si>
-  <si>
-    <t>RH/N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RH/N </t>
-  </si>
-  <si>
-    <t>Saber</t>
-  </si>
-  <si>
-    <t>HR/N</t>
-  </si>
-  <si>
-    <t>HR/G et N</t>
-  </si>
-  <si>
     <t>Deadline</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Certificat / document d'enregistrement du bâtiment 
+Certificat d'achèvement de construction — si applicable : OK
+Certificat / rapport d'inspection du bâtiment / OK
+Autorisation d'exploitation — si applicable / OK
+Plans architecturaux approuvés / IN PROGRESS
+Documents relatifs aux modifications/extensions NA
+Documents de sécurité incendie / OK
+Contrat de location — si MYC est locataire / IN PROGRESS
+Documents fournis par le propriétaire NA</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>Département technique</t>
+  </si>
+  <si>
+    <t>Supply chain</t>
+  </si>
+  <si>
+    <t>Finance</t>
   </si>
 </sst>
 </file>
@@ -673,7 +646,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -695,6 +668,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -726,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -763,12 +748,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1051,12 +1058,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85D68A6-C2D4-43FD-A68C-F605CD9701C8}">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.08984375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="61.26953125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" customWidth="1"/>
+    <col min="3" max="3" width="61.1796875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
     <col min="6" max="6" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1077,7 +1084,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="177.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1091,12 +1098,12 @@
         <v>6</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F2" s="16">
+        <v>111</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1105,18 +1112,18 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="16">
+        <v>9</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1125,18 +1132,18 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>109</v>
+      <c r="D4" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="16">
+        <v>102</v>
+      </c>
+      <c r="F4" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1145,18 +1152,18 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="D5" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1165,18 +1172,18 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="16">
+        <v>102</v>
+      </c>
+      <c r="F6" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1185,14 +1192,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="16">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="19">
         <v>46311</v>
       </c>
     </row>
@@ -1201,18 +1212,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="16">
+        <v>102</v>
+      </c>
+      <c r="F8" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1221,18 +1232,18 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F9" s="16">
+        <v>102</v>
+      </c>
+      <c r="F9" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1241,18 +1252,18 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="16">
+        <v>102</v>
+      </c>
+      <c r="F10" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1260,17 +1271,19 @@
       <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="16">
+      <c r="B11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="19">
         <v>46311</v>
       </c>
     </row>
@@ -1278,15 +1291,17 @@
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="8"/>
+      <c r="B12" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="20"/>
       <c r="D12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="16">
+        <v>9</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1295,18 +1310,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" s="16">
+        <v>102</v>
+      </c>
+      <c r="F13" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1315,18 +1330,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="16">
+        <v>102</v>
+      </c>
+      <c r="F14" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1335,18 +1350,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="16">
+        <v>102</v>
+      </c>
+      <c r="F15" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1355,16 +1370,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>10</v>
+        <v>33</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="E16" s="10"/>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1373,18 +1388,18 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="16">
+        <v>102</v>
+      </c>
+      <c r="F17" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1393,18 +1408,18 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F18" s="16">
+        <v>102</v>
+      </c>
+      <c r="F18" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1413,18 +1428,18 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F19" s="16">
+        <v>102</v>
+      </c>
+      <c r="F19" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1433,18 +1448,18 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F20" s="16">
+        <v>102</v>
+      </c>
+      <c r="F20" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1453,18 +1468,18 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" s="16">
+        <v>102</v>
+      </c>
+      <c r="F21" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1472,37 +1487,37 @@
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="16">
-        <v>46311</v>
-      </c>
+      <c r="B22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F23" s="16">
+        <v>102</v>
+      </c>
+      <c r="F23" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1511,18 +1526,18 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="16">
+        <v>102</v>
+      </c>
+      <c r="F24" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1531,18 +1546,18 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="E25" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F25" s="16">
+        <v>102</v>
+      </c>
+      <c r="F25" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1551,18 +1566,18 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>15</v>
+        <v>110</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" s="16">
+        <v>102</v>
+      </c>
+      <c r="F26" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1571,18 +1586,18 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="16">
+        <v>102</v>
+      </c>
+      <c r="F27" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1591,22 +1606,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="16">
+        <v>102</v>
+      </c>
+      <c r="F28" s="15">
         <v>46311</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="174" x14ac:dyDescent="0.35">
@@ -1614,18 +1629,18 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="16">
+        <v>102</v>
+      </c>
+      <c r="F29" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1634,18 +1649,18 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" s="16">
+        <v>102</v>
+      </c>
+      <c r="F30" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1653,37 +1668,37 @@
       <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="16">
-        <v>46311</v>
-      </c>
+      <c r="B31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="18"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F32" s="16">
+        <v>102</v>
+      </c>
+      <c r="F32" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1692,16 +1707,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="16">
+        <v>9</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1710,18 +1727,18 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F34" s="16">
+        <v>102</v>
+      </c>
+      <c r="F34" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1729,19 +1746,19 @@
       <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="16">
+      <c r="B35" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="19">
         <v>46311</v>
       </c>
     </row>
@@ -1750,18 +1767,18 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="16">
+        <v>102</v>
+      </c>
+      <c r="F36" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1770,22 +1787,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F37" s="16">
-        <v>46311</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>113</v>
+        <v>102</v>
+      </c>
+      <c r="F37" s="15">
+        <v>46311</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="174" x14ac:dyDescent="0.35">
@@ -1793,18 +1810,18 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F38" s="16">
+        <v>102</v>
+      </c>
+      <c r="F38" s="15">
         <v>46311</v>
       </c>
       <c r="G38" s="7"/>
@@ -1814,18 +1831,18 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F39" s="16">
+        <v>102</v>
+      </c>
+      <c r="F39" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1834,18 +1851,18 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F40" s="16">
+        <v>102</v>
+      </c>
+      <c r="F40" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1854,18 +1871,18 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F41" s="16">
+        <v>102</v>
+      </c>
+      <c r="F41" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1874,18 +1891,18 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F42" s="16">
+        <v>102</v>
+      </c>
+      <c r="F42" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1894,18 +1911,18 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F43" s="16">
+        <v>102</v>
+      </c>
+      <c r="F43" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1913,17 +1930,19 @@
       <c r="A44" s="7">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="16">
+      <c r="B44" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="19">
         <v>46311</v>
       </c>
     </row>
@@ -1932,18 +1951,18 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F45" s="16">
+        <v>102</v>
+      </c>
+      <c r="F45" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1952,18 +1971,18 @@
         <v>45</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F46" s="16">
+        <v>102</v>
+      </c>
+      <c r="F46" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1972,18 +1991,18 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F47" s="16">
+        <v>102</v>
+      </c>
+      <c r="F47" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -1991,17 +2010,19 @@
       <c r="A48" s="7">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="7"/>
-      <c r="F48" s="16">
+      <c r="B48" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="19">
         <v>46311</v>
       </c>
     </row>
@@ -2010,18 +2031,18 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F49" s="16">
+        <v>102</v>
+      </c>
+      <c r="F49" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -2030,18 +2051,18 @@
         <v>49</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F50" s="16">
+        <v>102</v>
+      </c>
+      <c r="F50" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -2050,18 +2071,18 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F51" s="16">
+        <v>102</v>
+      </c>
+      <c r="F51" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -2070,18 +2091,18 @@
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F52" s="16">
+        <v>102</v>
+      </c>
+      <c r="F52" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -2090,18 +2111,18 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F53" s="16">
+        <v>102</v>
+      </c>
+      <c r="F53" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -2110,18 +2131,18 @@
         <v>53</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F54" s="16">
+        <v>102</v>
+      </c>
+      <c r="F54" s="15">
         <v>46311</v>
       </c>
     </row>
@@ -2134,7 +2155,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
